--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104527_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104527_W8.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4436</v>
+        <v>7.6691</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0026</v>
+        <v>6.9819</v>
       </c>
       <c r="F2" t="n">
-        <v>0.441</v>
+        <v>0.6872</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6654</v>
+        <v>5.6461</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7157</v>
+        <v>0.7179</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9497</v>
+        <v>4.9282</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4584</v>
+        <v>7.4234</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6451</v>
+        <v>1.6375</v>
       </c>
       <c r="L2" t="n">
-        <v>5.8133</v>
+        <v>5.7859</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.793</v>
+        <v>-1.7774</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0977</v>
+        <v>0.3401</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0393</v>
+        <v>0.0624</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0584</v>
+        <v>0.2777</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0083</v>
+        <v>3.1022</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4718</v>
+        <v>1.9319</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5364</v>
+        <v>1.1703</v>
       </c>
       <c r="G3" t="n">
-        <v>1.483</v>
+        <v>1.4861</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8673</v>
+        <v>0.8646</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6158</v>
+        <v>0.6214</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8629</v>
+        <v>2.8461</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4821</v>
+        <v>1.4684</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3807</v>
+        <v>1.3778</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3798</v>
+        <v>-1.3601</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3003</v>
+        <v>0.3869</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6956</v>
+        <v>-0.2023</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9959</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0285</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9076</v>
+        <v>2.733</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3799</v>
+        <v>1.364</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5277</v>
+        <v>1.369</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0772</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7517</v>
+        <v>0.7552</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1021</v>
+        <v>2.0835</v>
       </c>
       <c r="K4" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4051</v>
+        <v>0.3943</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0248</v>
+        <v>-2.0062</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8698</v>
+        <v>0.706</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0393</v>
+        <v>0.0624</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8305</v>
+        <v>0.6437</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7264</v>
+        <v>2.5914</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6889</v>
+        <v>1.734</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0375</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2596</v>
+        <v>0.255</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1184</v>
+        <v>0.1151</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1413</v>
+        <v>0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6894</v>
+        <v>2.6625</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9382</v>
+        <v>0.9201</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7512</v>
+        <v>1.7425</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4298</v>
+        <v>-2.4075</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9185</v>
+        <v>0.7932</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2389</v>
+        <v>-0.1467</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1574</v>
+        <v>0.9399</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0085</v>
+        <v>1.489</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3759</v>
+        <v>0.4162</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3844</v>
+        <v>1.0728</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6524</v>
+        <v>0.9978</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3015</v>
+        <v>0.655</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9539</v>
+        <v>0.3428</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3093</v>
+        <v>1.9146</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9005</v>
+        <v>1.2443</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2098</v>
+        <v>0.6703</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3431</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2559</v>
+        <v>-0.3275</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3926</v>
+        <v>0.4425</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1603</v>
+        <v>-0.1326</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2323</v>
+        <v>0.575</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6415999999999999</v>
+        <v>1.4771</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0583</v>
+        <v>-0.1032</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6999</v>
+        <v>1.5803</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9966</v>
+        <v>-1.5242</v>
       </c>
       <c r="H7" t="n">
-        <v>0.658</v>
+        <v>0.0345</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3386</v>
+        <v>-1.5587</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9287</v>
+        <v>0.0779</v>
       </c>
       <c r="K7" t="n">
-        <v>1.257</v>
+        <v>0.4514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6717</v>
+        <v>-0.3735</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9321</v>
+        <v>-1.6022</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.599</v>
+        <v>-0.4169</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3331</v>
+        <v>-1.1852</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-3.6421</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>2.9592</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3965</v>
+        <v>0.4158</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6261</v>
+        <v>0.1925</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2296</v>
+        <v>0.2232</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>3.2684</v>
       </c>
       <c r="W7" t="n">
+        <v>3.2684</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.0927</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6008</v>
+        <v>0.913</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9091</v>
+        <v>-1.5562</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3083</v>
+        <v>2.4691</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6686</v>
+        <v>-1.6536</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7432</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0746</v>
+        <v>-1.9606</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5453</v>
+        <v>-1.3237</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3912</v>
+        <v>0.8963</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1541</v>
+        <v>-2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2139</v>
+        <v>-0.33</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1344</v>
+        <v>-0.5893</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0795</v>
+        <v>0.2593</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0236</v>
+        <v>0.2903</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0484</v>
+        <v>-0.0049</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0248</v>
+        <v>0.2951</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5053</v>
+        <v>0.8061</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0467</v>
+        <v>1.3585</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5414</v>
+        <v>-0.5524</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5905</v>
+        <v>0.5889</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2121</v>
+        <v>0.2152</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3785</v>
+        <v>0.3737</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5336</v>
+        <v>1.5189</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9275</v>
+        <v>0.9156</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9431</v>
+        <v>-0.93</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1001</v>
+        <v>0.3962</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4869</v>
+        <v>-0.1604</v>
       </c>
       <c r="U9" t="n">
-        <v>0.587</v>
+        <v>0.5565</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4654</v>
+        <v>0.2132</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.709</v>
+        <v>0.5545</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1744</v>
+        <v>-0.3414</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5115</v>
+        <v>-0.6639</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0346</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5461</v>
+        <v>0.0745</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1111</v>
+        <v>1.5291</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4604</v>
+        <v>0.3825</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3494</v>
+        <v>1.1467</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6225</v>
+        <v>-2.1931</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4258</v>
+        <v>-1.1209</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1967</v>
+        <v>-1.0722</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9488</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6206</v>
+        <v>-0.4204</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4688</v>
+        <v>-0.3812</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1518</v>
+        <v>-0.0392</v>
       </c>
       <c r="V10" t="n">
-        <v>3.278</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>3.278</v>
+        <v>0.5447</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4346</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2549</v>
+        <v>0.9979</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6895</v>
+        <v>-1.8754</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3302</v>
+        <v>-1.3338</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7705</v>
+        <v>-0.7752</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5598</v>
+        <v>-0.5586</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1592</v>
+        <v>0.1409</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3605</v>
+        <v>-0.3727</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4894</v>
+        <v>-1.4747</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0395</v>
+        <v>0.5865</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4567</v>
+        <v>0.2228</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5828</v>
+        <v>0.3637</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3776</v>
+        <v>-1.2334</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0706</v>
+        <v>0.0535</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4482</v>
+        <v>-1.2869</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0852</v>
+        <v>-0.0939</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3592</v>
+        <v>-1.3613</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2741</v>
+        <v>1.2674</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7665</v>
+        <v>1.74</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4298</v>
+        <v>-0.4417</v>
       </c>
       <c r="L12" t="n">
-        <v>2.1963</v>
+        <v>2.1816</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8516</v>
+        <v>-1.8339</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1198</v>
+        <v>0.2671</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1603</v>
+        <v>0.1833</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0405</v>
+        <v>0.0838</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.4953</v>
+        <v>18.8832</v>
       </c>
       <c r="E13" t="n">
-        <v>12.6813</v>
+        <v>13.733</v>
       </c>
       <c r="F13" t="n">
-        <v>4.813900000000001</v>
+        <v>5.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8245</v>
+        <v>3.781699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7864</v>
+        <v>0.7896000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0384</v>
+        <v>2.9922</v>
       </c>
       <c r="J13" t="n">
-        <v>20.8479</v>
+        <v>20.6132</v>
       </c>
       <c r="K13" t="n">
-        <v>8.587300000000001</v>
+        <v>8.4786</v>
       </c>
       <c r="L13" t="n">
-        <v>12.2604</v>
+        <v>12.1348</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.0231</v>
+        <v>-16.8319</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.8009</v>
+        <v>-7.688899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.222</v>
+        <v>-9.142800000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>9.0733</v>
+        <v>9.105300000000002</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.2808</v>
+        <v>-19.3487</v>
       </c>
       <c r="R13" t="n">
-        <v>28.3542</v>
+        <v>28.45379999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>2.797600000000001</v>
+        <v>4.2042</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.7088</v>
+        <v>-0.3047</v>
       </c>
       <c r="U13" t="n">
-        <v>4.5064</v>
+        <v>4.508599999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>1.799599999999999</v>
+        <v>1.7919</v>
       </c>
       <c r="W13" t="n">
-        <v>12.8229</v>
+        <v>12.773</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.0233</v>
+        <v>-10.9811</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SYLLA</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6445</v>
+        <v>1.8757</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6308</v>
+        <v>3.1931</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9863</v>
+        <v>-1.3175</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2492</v>
+        <v>2.2984</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3131</v>
+        <v>1.6976</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0639</v>
+        <v>0.6008</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9605</v>
+        <v>5.8635</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8485</v>
+        <v>2.8473</v>
       </c>
       <c r="L14" t="n">
-        <v>0.112</v>
+        <v>3.0162</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7113</v>
+        <v>-3.5651</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5354</v>
+        <v>-1.1497</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1759</v>
+        <v>-2.4154</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4537</v>
+        <v>3.1868</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3953</v>
+        <v>-0.5609</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5777</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1824</v>
+        <v>0.1503</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3777</v>
+        <v>1.5847</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0415</v>
+        <v>1.9936</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.4089</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0829</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.524</v>
+        <v>2.5082</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.6069</v>
+        <v>-2.6053</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6032</v>
+        <v>1.5628</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3279</v>
+        <v>3.2987</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.7247</v>
+        <v>-1.7359</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6861</v>
+        <v>-1.6599</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1272</v>
+        <v>-0.9116</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9739</v>
+        <v>-0.9758</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1534</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>A. SYLLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2375</v>
+        <v>1.4306</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7588</v>
+        <v>2.1525</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5212</v>
+        <v>-0.7219</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2905</v>
+        <v>0.2552</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7013</v>
+        <v>0.3131</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5891999999999999</v>
+        <v>-0.0578</v>
       </c>
       <c r="J16" t="n">
-        <v>5.8901</v>
+        <v>0.9563</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8675</v>
+        <v>0.8446</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0227</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.5996</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1662</v>
+        <v>-0.5315</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4335</v>
+        <v>-0.1695</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1757</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1871</v>
+        <v>0.1754</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1825</v>
+        <v>0.1067</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0046</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7876</v>
+        <v>0.5433</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1873</v>
+        <v>2.1497</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3997</v>
+        <v>-1.6063</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2639</v>
+        <v>-0.2634</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4372</v>
+        <v>-0.4393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1733</v>
+        <v>0.1759</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7209</v>
+        <v>1.6979</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1936</v>
+        <v>0.1789</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5273</v>
+        <v>1.519</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9848</v>
+        <v>-1.9613</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2395</v>
+        <v>-0.4923</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9043</v>
+        <v>-0.9061</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.4138</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1212</v>
+        <v>-2.1075</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1283</v>
+        <v>-1.0447</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1181</v>
+        <v>-0.7351</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0102</v>
+        <v>-0.3097</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.942</v>
+        <v>-1.9377</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.58</v>
+        <v>-0.5856</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.362</v>
+        <v>-1.3521</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3255</v>
+        <v>0.3106</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1763</v>
+        <v>0.1616</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2675</v>
+        <v>-2.2483</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9511</v>
+        <v>0.7839</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8075</v>
+        <v>-0.0166</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1435</v>
+        <v>0.8005</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.459</v>
+        <v>-1.1094</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0742</v>
+        <v>0.3679</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3849</v>
+        <v>-1.4773</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7318</v>
+        <v>1.7338</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1919</v>
+        <v>-2.1914</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9237</v>
+        <v>3.9252</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8848</v>
+        <v>3.8662</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4515</v>
+        <v>-1.4586</v>
       </c>
       <c r="L19" t="n">
-        <v>5.3363</v>
+        <v>5.3249</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.153</v>
+        <v>-2.1325</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>0.036</v>
+        <v>0.3845</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5565</v>
+        <v>-0.0838</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5925</v>
+        <v>0.4683</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4941</v>
+        <v>-1.2152</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6723</v>
+        <v>-0.5744</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8219</v>
+        <v>-0.6408</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6083</v>
+        <v>0.6153</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4979</v>
+        <v>-0.4915</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1062</v>
+        <v>1.1068</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7831</v>
+        <v>1.7742</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1749</v>
+        <v>-1.1588</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2631</v>
+        <v>0.0117</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0847</v>
+        <v>0.2418</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2057</v>
+        <v>-2.5705</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4686</v>
+        <v>-2.002</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7371</v>
+        <v>-0.5685</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2278</v>
+        <v>-0.2268</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0677</v>
+        <v>1.0738</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2955</v>
+        <v>-1.3007</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8633</v>
+        <v>1.8343</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0607</v>
+        <v>2.0512</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1974</v>
+        <v>-0.2169</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0911</v>
+        <v>-2.0612</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.8976</v>
+        <v>-5.9184</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2825</v>
+        <v>-0.6317</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3266</v>
+        <v>-0.7994</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0441</v>
+        <v>0.1677</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1287</v>
+        <v>-4.0625</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7183</v>
+        <v>-4.7409</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5896</v>
+        <v>0.6784</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7498</v>
+        <v>-0.7341</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0968</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.653</v>
+        <v>-0.6446</v>
       </c>
       <c r="J22" t="n">
-        <v>0.441</v>
+        <v>0.4392</v>
       </c>
       <c r="K22" t="n">
-        <v>0.329</v>
+        <v>0.3275</v>
       </c>
       <c r="L22" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1908</v>
+        <v>-1.1733</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8837</v>
+        <v>-0.8245</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5565</v>
+        <v>-0.5576</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3273</v>
+        <v>-0.2669</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1172</v>
+        <v>-5.5622</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3078</v>
+        <v>-2.9726</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8094</v>
+        <v>-2.5896</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5932</v>
+        <v>-2.5844</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9913</v>
+        <v>-0.9909</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6019</v>
+        <v>-1.5935</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.483</v>
+        <v>-0.494</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5625</v>
+        <v>-0.5662</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1103</v>
+        <v>-2.0904</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0708</v>
+        <v>-1.0631</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5901</v>
+        <v>-0.0476</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5565</v>
+        <v>-0.2023</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0336</v>
+        <v>0.1546</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2662</v>
+        <v>-6.5692</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3095</v>
+        <v>-3.9818</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9567</v>
+        <v>-2.5874</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8449</v>
+        <v>-2.841</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5974</v>
+        <v>-1.5942</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2475</v>
+        <v>-1.2468</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9664</v>
+        <v>-0.9795</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8785</v>
+        <v>-1.8615</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6067</v>
+        <v>0.0929</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1198</v>
+        <v>0.2254</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.4953</v>
+        <v>-16.6994</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8142</v>
+        <v>-5.149999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.6812</v>
+        <v>-11.5495</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.8247</v>
+        <v>-3.7818</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7863999999999992</v>
+        <v>-0.7895999999999995</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.0383</v>
+        <v>-2.9921</v>
       </c>
       <c r="J25" t="n">
-        <v>17.023</v>
+        <v>16.8315</v>
       </c>
       <c r="K25" t="n">
-        <v>7.801000000000002</v>
+        <v>7.688800000000002</v>
       </c>
       <c r="L25" t="n">
-        <v>9.222299999999999</v>
+        <v>9.142600000000002</v>
       </c>
       <c r="M25" t="n">
-        <v>-20.8479</v>
+        <v>-20.6134</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.587399999999999</v>
+        <v>-8.4785</v>
       </c>
       <c r="O25" t="n">
-        <v>-12.2605</v>
+        <v>-12.1349</v>
       </c>
       <c r="P25" t="n">
-        <v>-9.0733</v>
+        <v>-9.1052</v>
       </c>
       <c r="Q25" t="n">
-        <v>-28.354</v>
+        <v>-28.4539</v>
       </c>
       <c r="R25" t="n">
-        <v>19.2809</v>
+        <v>19.3488</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.7975</v>
+        <v>-2.0202</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.5063</v>
+        <v>-4.508800000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7085</v>
+        <v>2.4883</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.7998</v>
+        <v>-1.7921</v>
       </c>
       <c r="W25" t="n">
-        <v>11.0232</v>
+        <v>10.981</v>
       </c>
       <c r="X25" t="n">
-        <v>-12.823</v>
+        <v>-12.7731</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104527_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104527_W8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-10.9811</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.1075</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104527_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-12.7731</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
